--- a/public/template-output-repair.xlsx
+++ b/public/template-output-repair.xlsx
@@ -32,8 +32,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="9">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="58" formatCode="m/d/yy"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;Rp&quot;* #,##0.00_-;\-&quot;Rp&quot;* #,##0.00_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="0.000"/>
+    <numFmt numFmtId="181" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
+    <numFmt numFmtId="182" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -397,7 +405,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:AN2"/>
+  <cols>
+    <col min="1" max="1" customWidth="1" width="7"/>
+    <col min="2" max="2" customWidth="1" width="14"/>
+    <col min="3" max="3" customWidth="1" width="13"/>
+    <col min="4" max="4" customWidth="1" width="17"/>
+    <col min="5" max="5" customWidth="1" width="37"/>
+    <col min="6" max="6" customWidth="1" width="13"/>
+    <col min="7" max="7" customWidth="1" width="12"/>
+    <col min="8" max="8" customWidth="1" width="9"/>
+    <col min="9" max="9" customWidth="1" width="7"/>
+    <col min="10" max="10" customWidth="1" width="12"/>
+    <col min="11" max="11" customWidth="1" width="13"/>
+    <col min="12" max="12" customWidth="1" width="5"/>
+    <col min="13" max="13" customWidth="1" width="6"/>
+    <col min="14" max="14" customWidth="1" width="12"/>
+    <col min="15" max="15" customWidth="1" width="12"/>
+    <col min="16" max="16" customWidth="1" width="12"/>
+    <col min="17" max="17" customWidth="1" width="14"/>
+    <col min="18" max="18" customWidth="1" width="14"/>
+    <col min="19" max="19" customWidth="1" width="20"/>
+    <col min="20" max="20" customWidth="1" width="9"/>
+    <col min="21" max="21" customWidth="1" width="18.1428571428571"/>
+    <col min="22" max="22" customWidth="1" width="17"/>
+    <col min="23" max="23" customWidth="1" width="13"/>
+    <col min="24" max="24" customWidth="1" width="13"/>
+    <col min="25" max="25" customWidth="1" width="15"/>
+    <col min="26" max="26" customWidth="1" width="12"/>
+    <col min="27" max="27" customWidth="1" width="17"/>
+    <col min="28" max="28" customWidth="1" width="13"/>
+    <col min="29" max="29" customWidth="1" width="10"/>
+    <col min="30" max="30" customWidth="1" width="12"/>
+    <col min="31" max="31" customWidth="1" width="17"/>
+    <col min="32" max="32" customWidth="1" width="18"/>
+    <col min="33" max="33" customWidth="1" width="20.5714285714286"/>
+    <col min="38" max="38" customWidth="1" width="10.5714285714286"/>
+    <col min="39" max="39" customWidth="1" width="9.57142857142857"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -416,140 +461,115 @@
         <v>NAME</v>
       </c>
       <c r="F1" t="str">
+        <v>LENGTH SIDE</v>
+      </c>
+      <c r="G1" t="str">
+        <v>WIDTH SIDE</v>
+      </c>
+      <c r="H1" t="str">
         <v>DIAM MM</v>
       </c>
-      <c r="G1" t="str">
+      <c r="I1" t="str">
         <v>TEBAL</v>
       </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>PANJANG</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
         <v>Work Centre</v>
       </c>
-      <c r="J1" t="str">
+      <c r="L1" t="str">
         <v>Mvt</v>
       </c>
-      <c r="K1" t="str">
+      <c r="M1" t="str">
         <v>SLOC</v>
       </c>
-      <c r="L1" t="str">
+      <c r="N1" t="str">
         <v>BATCH</v>
       </c>
-      <c r="M1" t="str">
+      <c r="O1" t="str">
         <v>GR Qty Pcs</v>
       </c>
-      <c r="N1" t="str">
+      <c r="P1" t="str">
         <v>GI Qty Pcs</v>
       </c>
-      <c r="O1" t="str">
+      <c r="Q1" t="str">
+        <v>GR Base Unit</v>
+      </c>
+      <c r="R1" t="str">
+        <v>GI Base Unit</v>
+      </c>
+      <c r="S1" t="str">
         <v>MATERIAL NUMBER</v>
       </c>
-      <c r="P1" t="str">
+      <c r="T1" t="str">
+        <v>% GR/GI</v>
+      </c>
+      <c r="U1" t="str">
+        <v>SETL</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Entry Date</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Trans. Loc.</v>
+      </c>
+      <c r="X1" t="str">
         <v>User name</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="Y1" t="str">
+        <v>Material Doc.</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>Period Pst</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>Time of Entry</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>Cost Centre</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>Qty SETL</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>LABELID</v>
+      </c>
+      <c r="AE1" t="str">
         <v>Doc.Date</v>
       </c>
-      <c r="R1" t="str">
+      <c r="AF1" t="str">
+        <v>HEAT NO.</v>
+      </c>
+      <c r="AG1" t="str">
         <v>REMARK</v>
       </c>
-      <c r="S1" t="str">
+      <c r="AH1" t="str">
+        <v>XX</v>
+      </c>
+      <c r="AI1" t="str">
         <v>Panjang Pipa</v>
       </c>
-      <c r="T1" t="str">
+      <c r="AJ1" t="str">
         <v>ST/LT</v>
       </c>
-      <c r="U1" t="str">
+      <c r="AK1" t="str">
         <v>Gudang</v>
       </c>
-      <c r="V1" t="str">
+      <c r="AL1" t="str">
         <v>Bulan</v>
       </c>
-      <c r="W1" t="str">
+      <c r="AM1" t="str">
         <v>Tonase (Kg)</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AN1" t="str">
         <v>Qty (pcs)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>1105</v>
-      </c>
-      <c r="B2" t="str">
-        <v>500000434115</v>
-      </c>
-      <c r="C2" t="str">
-        <v>REP-501</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2026-09-18</v>
-      </c>
-      <c r="E2" t="str">
-        <v>PT. CHANDRA NUGRAHA</v>
-      </c>
-      <c r="F2" t="str">
-        <v>28,60</v>
-      </c>
-      <c r="G2" t="str">
-        <v>1,50</v>
-      </c>
-      <c r="H2" t="str">
-        <v>267,00mm</v>
-      </c>
-      <c r="I2" t="str">
-        <v>REP-501</v>
-      </c>
-      <c r="J2" t="str">
-        <v>101</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Shift 1</v>
-      </c>
-      <c r="L2" t="str">
-        <v>5261725HEC</v>
-      </c>
-      <c r="M2">
-        <v>300</v>
-      </c>
-      <c r="N2">
-        <v>5</v>
-      </c>
-      <c r="O2" t="str">
-        <v>XCB10BCA0150+02670</v>
-      </c>
-      <c r="P2" t="str">
-        <v>HADAD</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>2026-09-18</v>
-      </c>
-      <c r="R2" t="str">
-        <v>Perbaikan sambungan las</v>
-      </c>
-      <c r="S2">
-        <v>267</v>
-      </c>
-      <c r="T2" t="str">
-        <v>St</v>
-      </c>
-      <c r="U2" t="str">
-        <v>Gd.05</v>
-      </c>
-      <c r="V2" t="str">
-        <v>September</v>
-      </c>
-      <c r="W2">
-        <v>80.4</v>
-      </c>
-      <c r="X2">
-        <v>305</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AN2"/>
   </ignoredErrors>
 </worksheet>
 </file>